--- a/data/trans_dic/P8_2_R-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/P8_2_R-Estudios-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con limitación a subir varios pisos</t>
+          <t>Población con limitación a subir varios pisos (tasa de respuesta: 99,98%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>27,21; 32,59</t>
+          <t>27,0; 32,82</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>29,84; 36,28</t>
+          <t>30,15; 36,58</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>30,09; 36,55</t>
+          <t>30,65; 37,6</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>31,77; 39,55</t>
+          <t>31,95; 39,71</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>42,88; 48,37</t>
+          <t>42,58; 48,25</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>46,18; 51,69</t>
+          <t>46,0; 51,84</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>45,55; 51,85</t>
+          <t>45,51; 52,43</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>51,74; 57,63</t>
+          <t>51,77; 57,43</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>36,66; 40,71</t>
+          <t>36,53; 40,59</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>40,21; 44,29</t>
+          <t>40,31; 44,51</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>39,9; 44,76</t>
+          <t>39,79; 44,74</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>44,53; 49,21</t>
+          <t>44,62; 49,17</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>5,66; 8,01</t>
+          <t>5,53; 7,91</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>7,62; 10,34</t>
+          <t>7,58; 10,3</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>8,23; 10,69</t>
+          <t>8,09; 10,8</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>12,41; 46,27</t>
+          <t>12,36; 47,46</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>7,41; 10,22</t>
+          <t>7,27; 10,11</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>10,93; 14,41</t>
+          <t>10,75; 14,36</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>12,11; 15,54</t>
+          <t>12,17; 15,41</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>9,81; 15,37</t>
+          <t>9,76; 15,32</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>6,79; 8,63</t>
+          <t>6,77; 8,54</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>9,58; 11,79</t>
+          <t>9,55; 11,71</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>10,59; 12,62</t>
+          <t>10,6; 12,63</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>12,66; 31,15</t>
+          <t>12,71; 33,59</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>4,51; 8,98</t>
+          <t>4,19; 8,75</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>5,07; 10,3</t>
+          <t>5,15; 10,43</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>5,63; 10,58</t>
+          <t>5,86; 10,78</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>5,2; 8,83</t>
+          <t>5,3; 8,71</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>7,56; 13,33</t>
+          <t>7,7; 13,77</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>5,99; 11,47</t>
+          <t>6,03; 11,32</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>6,27; 11,39</t>
+          <t>6,02; 11,2</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>7,51; 11,02</t>
+          <t>7,49; 10,98</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>6,48; 10,02</t>
+          <t>6,5; 10,19</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>6,13; 10,01</t>
+          <t>6,25; 9,85</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>6,52; 10,19</t>
+          <t>6,38; 9,96</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>6,71; 9,26</t>
+          <t>6,71; 9,16</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>12,84; 15,12</t>
+          <t>12,7; 15,13</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>14,34; 17,02</t>
+          <t>14,27; 16,8</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>13,26; 15,86</t>
+          <t>13,38; 15,78</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>14,89; 38,62</t>
+          <t>14,9; 37,86</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>21,77; 24,82</t>
+          <t>21,82; 24,75</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>24,1; 27,25</t>
+          <t>24,17; 27,09</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>21,33; 24,29</t>
+          <t>21,33; 24,42</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>17,07; 23,08</t>
+          <t>17,33; 22,98</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>17,7; 19,68</t>
+          <t>17,73; 19,57</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>19,75; 21,67</t>
+          <t>19,76; 21,72</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>17,85; 19,8</t>
+          <t>17,87; 19,71</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>17,84; 31,8</t>
+          <t>17,88; 31,17</t>
         </is>
       </c>
     </row>
@@ -1246,7 +1246,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con limitación a subir varios pisos</t>
+          <t>Población con limitación a subir varios pisos (tasa de respuesta: 99,98%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1504,62 +1504,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>280722; 336212</t>
+          <t>278535; 338660</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>290815; 353583</t>
+          <t>293811; 356497</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>226955; 275718</t>
+          <t>231186; 283632</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>163590; 203650</t>
+          <t>164506; 204461</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>563919; 636135</t>
+          <t>559922; 634552</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>617243; 690891</t>
+          <t>614930; 692939</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>453057; 515740</t>
+          <t>452709; 521532</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>390595; 435033</t>
+          <t>390818; 433527</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>860415; 955377</t>
+          <t>857341; 952517</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>929394; 1023671</t>
+          <t>931647; 1028718</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>697840; 782881</t>
+          <t>695909; 782545</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>565440; 624965</t>
+          <t>566658; 624343</t>
         </is>
       </c>
     </row>
@@ -1712,62 +1712,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>95883; 135636</t>
+          <t>93692; 133997</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>149350; 202649</t>
+          <t>148537; 201872</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>170826; 221911</t>
+          <t>167877; 224173</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>284316; 1059717</t>
+          <t>283012; 1086956</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>117644; 162308</t>
+          <t>115346; 160471</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>192089; 253355</t>
+          <t>188905; 252427</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>240685; 308962</t>
+          <t>242058; 306420</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>219507; 344030</t>
+          <t>218450; 342846</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>222831; 283051</t>
+          <t>222004; 280294</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>356253; 438454</t>
+          <t>355233; 435510</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>430535; 512946</t>
+          <t>430950; 513365</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>573188; 1410312</t>
+          <t>575518; 1521115</t>
         </is>
       </c>
     </row>
@@ -1920,62 +1920,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>24854; 49520</t>
+          <t>23085; 48246</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>24385; 49580</t>
+          <t>24780; 50176</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>30771; 57868</t>
+          <t>32054; 58943</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>33569; 57027</t>
+          <t>34218; 56239</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>36010; 63483</t>
+          <t>36696; 65614</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>27492; 52609</t>
+          <t>27677; 51903</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>34425; 62522</t>
+          <t>33056; 61523</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>49626; 72796</t>
+          <t>49440; 72512</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>66572; 102965</t>
+          <t>66820; 104709</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>57635; 94035</t>
+          <t>58731; 92543</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>71510; 111728</t>
+          <t>69978; 109199</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>87708; 120924</t>
+          <t>87626; 119721</t>
         </is>
       </c>
     </row>
@@ -2128,62 +2128,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>420700; 495339</t>
+          <t>416239; 495773</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>489931; 581398</t>
+          <t>487540; 573863</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>447711; 535657</t>
+          <t>451816; 533126</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>514037; 1332936</t>
+          <t>514077; 1306495</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>735747; 838704</t>
+          <t>737279; 836512</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>856378; 968339</t>
+          <t>858931; 962605</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>753248; 858064</t>
+          <t>753290; 862647</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>623564; 843130</t>
+          <t>633246; 839328</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>1178324; 1310043</t>
+          <t>1180066; 1302736</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>1376380; 1509846</t>
+          <t>1376963; 1513702</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>1233417; 1367877</t>
+          <t>1234849; 1361858</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>1267111; 2259192</t>
+          <t>1269964; 2214702</t>
         </is>
       </c>
     </row>
